--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>AI Engineer / Senior Platform Support Officer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53c61ac50aad63e</t>
+          <t>https://www.indeed.com/viewjob?jk=2833779a05dd416c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e53c61ac50aad63e</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Data Engineer (Tampa)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tapouts</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Venice, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
+          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c8f77340c6b511f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Arrow International</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c3c576bdca9fea</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b0c81573d731c6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Tapouts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Venice, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ARCHKEY SOLUTIONS</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fenton, MO, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
+          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Creative Global Consulting</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
+          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Syncreon Consulting</t>
+          <t>HarperCollins Canada and Harlequin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ConcertAI</t>
+          <t>ARCHKEY SOLUTIONS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>Fenton, MO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
+          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Creative Global Consulting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
+          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kafka API Gateway Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Syncreon Consulting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
+          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ConcertAI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
+          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,24 +1151,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
+          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Kafka API Gateway Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Python, Spark</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Flask Architect</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
+          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deltasoft Solutions LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Engineer III - AWS, Python, Spark</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Flask Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
+          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deltasoft Solutions LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Satlantis</t>
+          <t>come and see</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gainesville, FL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Platform Engineer - Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>S3, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee79c7f5d1c28258</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Satlantis</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Gainesville, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
+          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI &amp; Cloud Platform Consultant Expert</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ELT, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03afdcd6cea2e3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
+          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,102 +2246,102 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
+          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>AI &amp; Cloud Platform Consultant Expert</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CX Data Labs</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,172 +2351,172 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
+          <t>https://www.indeed.com/viewjob?jk=03afdcd6cea2e3b1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TMA SYSTEMS</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, NoSQL, Data Modeling, Power BI, CI/CD</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49da61e6b6b0755f</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TMA SYSTEMS</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, NoSQL, Data Modeling, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965b34c898c4918a</t>
+          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer / Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TruStartIT LLC</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Integrations Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Vista Higher Learning</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
+          <t>https://www.indeed.com/viewjob?jk=4987d7a71ebb3a76</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>CX Data Labs</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Senior Databricks Developer / Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AGDATA LP</t>
+          <t>TruStartIT LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6670494253881e</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Senior Bizops Engineer-1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b2ed1b7ac0e776d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Senior Machine Learning Engineers</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Cloud Storage, Scala, Data Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=927c7b77a89e979d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AGDATA LP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6670494253881e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,42 +3356,42 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Control Plane</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Aerospike</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,67 +3436,67 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>GCP Cloud Infrastructure Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
+          <t>https://www.indeed.com/viewjob?jk=fae4f5e0a1b671f8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Architect / Cloud Architect (Architecture Review &amp; Advisory) CONTRACT - REMOTE</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f088c401f3aecdf0</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Client Service</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07f3cfe8d1d836</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Associate Software Engineer, Platform – COCore</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Spark, Oracle, PostgreSQL, Terraform, Git</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ed0d4d942ded9c</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - API Solutions</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Athena, API Gateway, ECS, RDS, Spark, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bcf2915fd9bd1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer - Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Scala Architect</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Westerra Credit Union</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,17 +4021,507 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>AMH</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Chantilly, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer New</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Chantilly, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer-AI</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Thomson Reuters</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SS&amp;C</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer (Multi-Cloud &amp; AI Adoption)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Hyve Solutions</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61cdbfe08b450503</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Data Architect / Cloud Architect (Architecture Review &amp; Advisory) CONTRACT - REMOTE</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Broadridge</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Newark, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, DynamoDB, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f088c401f3aecdf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Client Service</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Fanatics</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da07f3cfe8d1d836</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer, Platform – COCore</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Athena, S3, RDS, Spark, Oracle, PostgreSQL, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99ed0d4d942ded9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>HealthEdge Software, Inc.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Data Engineer - Developer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Scala Architect</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - API Solutions</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, Athena, API Gateway, ECS, RDS, Spark, Scala, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bcf2915fd9bd1ef</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.7</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ac562fdbccfcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5ffe3e0696e29a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior Platform Support Officer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>25.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2833779a05dd416c</t>
+          <t>https://www.indeed.com/viewjob?jk=31ac562fdbccfcbb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>AI Engineer / Senior Platform Support Officer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53c61ac50aad63e</t>
+          <t>https://www.indeed.com/viewjob?jk=2833779a05dd416c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (ServiceNow)</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hotwire Communications</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
+          <t>https://www.indeed.com/viewjob?jk=e53c61ac50aad63e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (Tampa)</t>
+          <t>Senior Software Engineer (ServiceNow)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Hotwire Communications</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Data Engineer (Tampa)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c8f77340c6b511f</t>
+          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
         </is>
       </c>
     </row>
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b0c81573d731c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4c8f77340c6b511f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tapouts</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Venice, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b0c81573d731c6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tapouts</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Venice, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
+          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HarperCollins Canada and Harlequin</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
+          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARCHKEY SOLUTIONS</t>
+          <t>HarperCollins Canada and Harlequin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fenton, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Creative Global Consulting</t>
+          <t>ARCHKEY SOLUTIONS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fenton, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Creative Global Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
+          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Syncreon Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ConcertAI</t>
+          <t>Syncreon Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
+          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ConcertAI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
+          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kafka API Gateway Engineer</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
+          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Kafka API Gateway Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
+          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Python, Spark</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Flask Architect</t>
+          <t>Software Engineer III - AWS, Python, Spark</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
+          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Flask Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deltasoft Solutions LLC</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deltasoft Solutions LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>come and see</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>come and see</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Infrastructure Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S3, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee79c7f5d1c28258</t>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Satlantis</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gainesville, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Platform Engineer - Associate</t>
+          <t>Senior AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>S3, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ee79c7f5d1c28258</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Satlantis</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Gainesville, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
+          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
+          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
+          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
+          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI &amp; Cloud Platform Consultant Expert</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ELT, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03afdcd6cea2e3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,94 +2386,94 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>AI &amp; Cloud Platform Consultant Expert</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=03afdcd6cea2e3b1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,29 +2551,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Integrations Architect</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Vista Higher Learning</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4987d7a71ebb3a76</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Integrations Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CX Data Labs</t>
+          <t>Vista Higher Learning</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
+          <t>https://www.indeed.com/viewjob?jk=4987d7a71ebb3a76</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer / Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TruStartIT LLC</t>
+          <t>CX Data Labs</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Senior Databricks Developer / Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>TruStartIT LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Bizops Engineer-1</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b2ed1b7ac0e776d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineers</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Cloud Storage, Scala, Data Modeling, ETL, MLOps</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927c7b77a89e979d</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AGDATA LP</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6670494253881e</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Senior Bizops Engineer-1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=4b2ed1b7ac0e776d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineers</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Cloud Storage, Scala, Data Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,19 +3261,19 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=927c7b77a89e979d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>AGDATA LP</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3282,11 +3282,11 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,59 +3296,59 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6670494253881e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Cloud Storage, Spark, Scala, Kafka, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=7d74a8c2e0b3bc97</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GCP Cloud Infrastructure Architect</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae4f5e0a1b671f8</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>GCP Cloud Infrastructure Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=fae4f5e0a1b671f8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Services</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Control Plane</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Aerospike</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,67 +3926,67 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Multi-Cloud &amp; AI Adoption)</t>
+          <t>Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Hyve Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cdbfe08b450503</t>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Architect / Cloud Architect (Architecture Review &amp; Advisory) CONTRACT - REMOTE</t>
+          <t>Senior Platform Engineer-AI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f088c401f3aecdf0</t>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Client Service</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07f3cfe8d1d836</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Associate Software Engineer, Platform – COCore</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Spark, Oracle, PostgreSQL, Terraform, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ed0d4d942ded9c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer (Multi-Cloud &amp; AI Adoption)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Hyve Solutions</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=61cdbfe08b450503</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer - Developer</t>
+          <t>Data Architect / Cloud Architect (Architecture Review &amp; Advisory) CONTRACT - REMOTE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
+          <t>https://www.indeed.com/viewjob?jk=f088c401f3aecdf0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Scala Architect</t>
+          <t>Senior Software Engineer – Client Service</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,14 +4486,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=da07f3cfe8d1d836</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - API Solutions</t>
+          <t>Associate Software Engineer, Platform – COCore</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4511,15 +4511,155 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
+          <t>AWS, Lambda, Athena, S3, RDS, Spark, Oracle, PostgreSQL, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99ed0d4d942ded9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>HealthEdge Software, Inc.</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Data Engineer - Developer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Scala Architect</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - API Solutions</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
           <t>AWS, Athena, API Gateway, ECS, RDS, Spark, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7bcf2915fd9bd1ef</t>
         </is>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (ServiceNow)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hotwire Communications</t>
+          <t>National Rural Water Association</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Duncan, OK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf4aa616b7efc0f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (Tampa)</t>
+          <t>Senior Software Engineer (ServiceNow)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Hotwire Communications</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Data Engineer (Tampa)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c8f77340c6b511f</t>
+          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
         </is>
       </c>
     </row>
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b0c81573d731c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4c8f77340c6b511f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tapouts</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Venice, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b0c81573d731c6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tapouts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Venice, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
+          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HarperCollins Canada and Harlequin</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
+          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ARCHKEY SOLUTIONS</t>
+          <t>HarperCollins Canada and Harlequin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fenton, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,69 +1011,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Creative Global Consulting</t>
+          <t>ARCHKEY SOLUTIONS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fenton, MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Creative Global Consulting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
+          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Syncreon Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ConcertAI</t>
+          <t>Syncreon Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
+          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ConcertAI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
+          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kafka API Gateway Engineer</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
+          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Kafka API Gateway Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
+          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Python, Spark</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Flask Architect</t>
+          <t>Software Engineer III - AWS, Python, Spark</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
+          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Flask Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deltasoft Solutions LLC</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deltasoft Solutions LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>come and see</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>come and see</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Infrastructure Engineer</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>S3, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee79c7f5d1c28258</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
+          <t>Senior AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Satlantis</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gainesville, FL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, ETL, ELT</t>
+          <t>S3, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
+          <t>https://www.indeed.com/viewjob?jk=ee79c7f5d1c28258</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Platform Engineer - Associate</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Satlantis</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Gainesville, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
+          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
+          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
+          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
+          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI &amp; Cloud Platform Consultant Expert</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ELT, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03afdcd6cea2e3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,94 +2491,94 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>AI &amp; Cloud Platform Consultant Expert</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=03afdcd6cea2e3b1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,29 +2656,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Integrations Architect</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Vista Higher Learning</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4987d7a71ebb3a76</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Integrations Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CX Data Labs</t>
+          <t>Vista Higher Learning</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
+          <t>https://www.indeed.com/viewjob?jk=4987d7a71ebb3a76</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer / Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TruStartIT LLC</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CX Data Labs</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
+          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Senior Databricks Developer / Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>TruStartIT LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
         </is>
       </c>
     </row>
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>Blue Sky Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Bizops Engineer-1</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b2ed1b7ac0e776d</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineers</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Cloud Storage, Scala, Data Modeling, ETL, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927c7b77a89e979d</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AGDATA LP</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6670494253881e</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,42 +3321,42 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Spark, Scala, Kafka, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d74a8c2e0b3bc97</t>
+          <t>https://www.indeed.com/viewjob?jk=688b84fca2804c71</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Senior Bizops Engineer-1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,102 +3436,102 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b2ed1b7ac0e776d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Senior Machine Learning Engineers</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Cloud Storage, Scala, Data Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=927c7b77a89e979d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>AGDATA LP</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6670494253881e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Cloud Storage, Spark, Scala, Kafka, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7d74a8c2e0b3bc97</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GCP Cloud Infrastructure Architect</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae4f5e0a1b671f8</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>GCP Cloud Infrastructure Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=fae4f5e0a1b671f8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior API Test Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=443bfd5538b7629d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Services</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Control Plane</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Aerospike</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,67 +4066,67 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Multi-Cloud &amp; AI Adoption)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Hyve Solutions</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cdbfe08b450503</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Architect / Cloud Architect (Architecture Review &amp; Advisory) CONTRACT - REMOTE</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f088c401f3aecdf0</t>
+          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Client Service</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07f3cfe8d1d836</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Associate Software Engineer, Platform – COCore</t>
+          <t>Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Spark, Oracle, PostgreSQL, Terraform, Git</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ed0d4d942ded9c</t>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer-AI</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer - Developer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Scala Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - API Solutions</t>
+          <t>Senior Platform Engineer (Multi-Cloud &amp; AI Adoption)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Hyve Solutions</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,15 +4651,260 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61cdbfe08b450503</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Data Architect / Cloud Architect (Architecture Review &amp; Advisory) CONTRACT - REMOTE</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Broadridge</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Newark, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, DynamoDB, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f088c401f3aecdf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Client Service</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Fanatics</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da07f3cfe8d1d836</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer, Platform – COCore</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Athena, S3, RDS, Spark, Oracle, PostgreSQL, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99ed0d4d942ded9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>HealthEdge Software, Inc.</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Data Engineer - Developer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Scala Architect</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - API Solutions</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
           <t>AWS, Athena, API Gateway, ECS, RDS, Spark, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7bcf2915fd9bd1ef</t>
         </is>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Software Engineer III - AWS, Python, Spark</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Python, Spark</t>
+          <t>Flask Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
+          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Flask Architect</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
+          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Deltasoft Solutions LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deltasoft Solutions LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>come and see</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>come and see</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
+          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>Senior AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>S3, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=ee79c7f5d1c28258</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AI Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>S3, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee79c7f5d1c28258</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Satlantis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Gainesville, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
+          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Satlantis</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gainesville, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Platform Engineer - Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
+          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
+          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
+          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
+          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
+          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
+          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>AI &amp; Cloud Platform Consultant Expert</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=03afdcd6cea2e3b1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI &amp; Cloud Platform Consultant Expert</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03afdcd6cea2e3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Integrations Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>Vista Higher Learning</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=4987d7a71ebb3a76</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Integrations Architect</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Vista Higher Learning</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4987d7a71ebb3a76</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,54 +2841,54 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CX Data Labs</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CX Data Labs</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
         </is>
       </c>
     </row>
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
+          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Databricks Developer / Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>TruStartIT LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer / Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TruStartIT LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Blue Sky Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
+          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Blue Sky Technology Solutions LLC</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=688b84fca2804c71</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688b84fca2804c71</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Bizops Engineer-1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b2ed1b7ac0e776d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Bizops Engineer-1</t>
+          <t>Senior Machine Learning Engineers</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Cloud Storage, Scala, Data Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b2ed1b7ac0e776d</t>
+          <t>https://www.indeed.com/viewjob?jk=927c7b77a89e979d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineers</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>AGDATA LP</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Cloud Storage, Scala, Data Modeling, ETL, MLOps</t>
+          <t>Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927c7b77a89e979d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6670494253881e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AGDATA LP</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, S3, RDS, Cloud Storage, Spark, Scala, Kafka, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6670494253881e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d74a8c2e0b3bc97</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Spark, Scala, Kafka, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d74a8c2e0b3bc97</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>GCP Cloud Infrastructure Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=fae4f5e0a1b671f8</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GCP Cloud Infrastructure Architect</t>
+          <t>Senior API Test Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae4f5e0a1b671f8</t>
+          <t>https://www.indeed.com/viewjob?jk=443bfd5538b7629d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior API Test Engineer</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443bfd5538b7629d</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Services</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Control Plane</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Aerospike</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,14 +4451,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>Senior Platform Engineer-AI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Platform Engineer (Multi-Cloud &amp; AI Adoption)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hyve Solutions</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+          <t>https://www.indeed.com/viewjob?jk=61cdbfe08b450503</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Multi-Cloud &amp; AI Adoption)</t>
+          <t>Data Architect / Cloud Architect (Architecture Review &amp; Advisory) CONTRACT - REMOTE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Hyve Solutions</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cdbfe08b450503</t>
+          <t>https://www.indeed.com/viewjob?jk=f088c401f3aecdf0</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Architect / Cloud Architect (Architecture Review &amp; Advisory) CONTRACT - REMOTE</t>
+          <t>Senior Software Engineer – Client Service</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f088c401f3aecdf0</t>
+          <t>https://www.indeed.com/viewjob?jk=da07f3cfe8d1d836</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Client Service</t>
+          <t>Associate Software Engineer, Platform – COCore</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Athena, S3, RDS, Spark, Oracle, PostgreSQL, Terraform, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07f3cfe8d1d836</t>
+          <t>https://www.indeed.com/viewjob?jk=99ed0d4d942ded9c</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Associate Software Engineer, Platform – COCore</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Spark, Oracle, PostgreSQL, Terraform, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ed0d4d942ded9c</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer - Developer</t>
+          <t>Scala Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
+          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Scala Architect</t>
+          <t>Senior Software Engineer - API Solutions</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Athena, API Gateway, ECS, RDS, Spark, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4870,41 +4870,6 @@
         </is>
       </c>
       <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - API Solutions</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>athenahealth</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, Athena, API Gateway, ECS, RDS, Spark, Scala, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7bcf2915fd9bd1ef</t>
         </is>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
+          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
+          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>HarperCollins Canada and Harlequin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HarperCollins Canada and Harlequin</t>
+          <t>ARCHKEY SOLUTIONS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fenton, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,69 +1011,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
+          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ARCHKEY SOLUTIONS</t>
+          <t>Creative Global Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fenton, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
+          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Creative Global Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Syncreon Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Syncreon Consulting</t>
+          <t>ConcertAI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
+          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ConcertAI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
+          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Kafka API Gateway Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kafka API Gateway Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
+          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Software Engineer III - AWS, Python, Spark</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Python, Spark</t>
+          <t>Flask Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
+          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Flask Architect</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
+          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Deltasoft Solutions LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deltasoft Solutions LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>come and see</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>come and see</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
+          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>S3, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee79c7f5d1c28258</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Infrastructure Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>CooperCompanies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Henrietta, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>S3, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee79c7f5d1c28258</t>
+          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Satlantis</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Gainesville, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
+          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Satlantis</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Gainesville, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Platform Engineer - Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
+          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>AI &amp; Cloud Platform Consultant Expert</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=03afdcd6cea2e3b1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI &amp; Cloud Platform Consultant Expert</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03afdcd6cea2e3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
@@ -2813,47 +2813,47 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CX Data Labs</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CX Data Labs</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
+          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Blue Sky Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,19 +3051,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
+          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Blue Sky Technology Solutions LLC</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>Senior Bizops Engineer-1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688b84fca2804c71</t>
+          <t>https://www.indeed.com/viewjob?jk=4b2ed1b7ac0e776d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Machine Learning Engineers</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Cloud Storage, Scala, Data Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=927c7b77a89e979d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=688b84fca2804c71</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Bizops Engineer-1</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b2ed1b7ac0e776d</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineers</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>AGDATA LP</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Cloud Storage, Scala, Data Modeling, ETL, MLOps</t>
+          <t>Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927c7b77a89e979d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6670494253881e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AGDATA LP</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6670494253881e</t>
+          <t>https://www.indeed.com/viewjob?jk=ff9e78b6f0cfc04d</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>GCP Cloud Infrastructure Architect</t>
+          <t>Senior API Test Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae4f5e0a1b671f8</t>
+          <t>https://www.indeed.com/viewjob?jk=443bfd5538b7629d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior API Test Engineer</t>
+          <t>GCP Cloud Infrastructure Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443bfd5538b7629d</t>
+          <t>https://www.indeed.com/viewjob?jk=fae4f5e0a1b671f8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Kissimmee, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=6e3d8c3773cd2c8c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Senior Engineer Technology</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb8d0b3951037c5</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Services</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Control Plane</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Aerospike</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,14 +4451,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Senior Platform Engineer-AI</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Multi-Cloud &amp; AI Adoption)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Hyve Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cdbfe08b450503</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Architect / Cloud Architect (Architecture Review &amp; Advisory) CONTRACT - REMOTE</t>
+          <t>Senior Platform Engineer (Multi-Cloud &amp; AI Adoption)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Hyve Solutions</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f088c401f3aecdf0</t>
+          <t>https://www.indeed.com/viewjob?jk=61cdbfe08b450503</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Client Service</t>
+          <t>Data Architect / Cloud Architect (Architecture Review &amp; Advisory) CONTRACT - REMOTE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07f3cfe8d1d836</t>
+          <t>https://www.indeed.com/viewjob?jk=f088c401f3aecdf0</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Associate Software Engineer, Platform – COCore</t>
+          <t>Senior Software Engineer – Client Service</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Spark, Oracle, PostgreSQL, Terraform, Git</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ed0d4d942ded9c</t>
+          <t>https://www.indeed.com/viewjob?jk=da07f3cfe8d1d836</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Developer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer - Developer</t>
+          <t>Associate Software Engineer, Platform – COCore</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Athena, S3, RDS, Spark, Oracle, PostgreSQL, Terraform, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
+          <t>https://www.indeed.com/viewjob?jk=99ed0d4d942ded9c</t>
         </is>
       </c>
     </row>
@@ -4872,6 +4872,41 @@
       <c r="G127" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7bcf2915fd9bd1ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Avaya</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93cc248964e1485d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Tapouts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Venice, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c8f77340c6b511f</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b0c81573d731c6</t>
+          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tapouts</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Venice, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
+          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>ARCHKEY SOLUTIONS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fenton, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
+          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>HarperCollins Canada and Harlequin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HarperCollins Canada and Harlequin</t>
+          <t>Creative Global Consulting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
+          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ARCHKEY SOLUTIONS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fenton, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Creative Global Consulting</t>
+          <t>Syncreon Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ConcertAI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
+          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Syncreon Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka API Gateway Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ConcertAI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kafka API Gateway Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
+          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Software Engineer III - AWS, Python, Spark</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
+          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Flask Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Python, Spark</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
+          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Flask Architect</t>
+          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deltasoft Solutions LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
+          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deltasoft Solutions LLC</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>come and see</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>come and see</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>CooperCompanies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Henrietta, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Infrastructure Engineer</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S3, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee79c7f5d1c28258</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Python/PySpark Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CooperCompanies</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Henrietta, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Satlantis</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gainesville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Platform Engineer - Associate</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
+          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
+          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
+          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
+          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,89 +2386,89 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI &amp; Cloud Platform Consultant Expert</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2477,38 +2477,38 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ELT, MLOps, CI/CD</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03afdcd6cea2e3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,77 +2621,77 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>CX Data Labs</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,54 +2701,54 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Integrations Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Vista Higher Learning</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2757,11 +2757,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4987d7a71ebb3a76</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Databricks Developer / Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>TruStartIT LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CX Data Labs</t>
+          <t>Blue Sky Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
+          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer / Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TruStartIT LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Blue Sky Technology Solutions LLC</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,137 +3191,137 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Bizops Engineer-1</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b2ed1b7ac0e776d</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineers</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Cloud Storage, Scala, Data Modeling, ETL, MLOps</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,67 +3331,67 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927c7b77a89e979d</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688b84fca2804c71</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AGDATA LP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6670494253881e</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff9e78b6f0cfc04d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Spark, Scala, Kafka, Oracle, SQL Server, CI/CD</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d74a8c2e0b3bc97</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior API Test Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443bfd5538b7629d</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GCP Cloud Infrastructure Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae4f5e0a1b671f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kissimmee, FL, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake, Tableau, Git, Python</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e3d8c3773cd2c8c</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Engineer Technology</t>
+          <t>Senior Platform Engineer-AI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb8d0b3951037c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Engineer - Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Scala Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Satlantis</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Gainesville, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, Kubernetes, Airflow, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,707 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data Ops Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Minnetonka, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud Services</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Roku</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Control Plane</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Aerospike</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>AWS DevOps Data Engineer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Railroad19</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Tesla</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>AMH</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Draper, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Chantilly, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer New</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Chantilly, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer-AI</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Thomson Reuters</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>SS&amp;C</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer (Multi-Cloud &amp; AI Adoption)</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Hyve Solutions</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Fremont, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61cdbfe08b450503</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Data Architect / Cloud Architect (Architecture Review &amp; Advisory) CONTRACT - REMOTE</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Broadridge</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Newark, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, DynamoDB, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f088c401f3aecdf0</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer – Client Service</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Fanatics</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da07f3cfe8d1d836</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Data Engineer - Developer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer, Platform – COCore</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>athenahealth</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Spark, Oracle, PostgreSQL, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99ed0d4d942ded9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Scala Architect</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - API Solutions</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>athenahealth</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, Athena, API Gateway, ECS, RDS, Spark, Scala, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7bcf2915fd9bd1ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Avaya</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93cc248964e1485d</t>
+          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tapouts</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Venice, CA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
+          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
+          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>HarperCollins Canada and Harlequin</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
         </is>
       </c>
     </row>
@@ -923,25 +923,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HarperCollins Canada and Harlequin</t>
+          <t>Creative Global Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
+          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Creative Global Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Syncreon Consulting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Syncreon Consulting</t>
+          <t>ConcertAI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
+          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ConcertAI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
+          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Kafka API Gateway Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kafka API Gateway Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
+          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Software Engineer III - AWS, Python, Spark</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Python, Spark</t>
+          <t>Flask Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
+          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Flask Architect</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
+          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Deltasoft Solutions LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deltasoft Solutions LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>come and see</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>come and see</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
+          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CooperCompanies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Henrietta, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CooperCompanies</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Henrietta, NY, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Platform Engineer - Associate</t>
+          <t>Python/PySpark Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Python/PySpark Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
+          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
+          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
+          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,42 +2236,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
+          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,94 +2281,94 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>CX Data Labs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CX Data Labs</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
+          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Databricks Developer / Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>TruStartIT LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,29 +2726,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Blue Sky Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer / Data Engineer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TruStartIT LLC</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Blue Sky Technology Solutions LLC</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Control Plane</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Aerospike</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
+          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Platform Engineer-AI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>Data Engineer - Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>Scala Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,182 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>SS&amp;C</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Data Engineer - Developer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Scala Architect</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Satlantis</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Gainesville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, Kubernetes, Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CooperCompanies</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Henrietta, NY, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>CooperCompanies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Henrietta, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
+          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,54 +2526,54 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CX Data Labs</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CX Data Labs</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
         </is>
       </c>
     </row>
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer / Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TruStartIT LLC</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
+          <t>Senior Databricks Developer / Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Blue Sky Technology Solutions LLC</t>
+          <t>TruStartIT LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Blue Sky Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Services</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Control Plane</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Aerospike</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer - Developer</t>
+          <t>Senior Platform Engineer-AI</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Scala Architect</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,15 +4021,85 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Data Engineer - Developer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Scala Architect</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
         </is>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (ServiceNow)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>National Rural Water Association</t>
+          <t>Hotwire Communications</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Duncan, OK, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf4aa616b7efc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (ServiceNow)</t>
+          <t>Data Engineer (Tampa)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hotwire Communications</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer (Tampa)</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
+          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
+          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
+          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>HarperCollins Canada and Harlequin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HarperCollins Canada and Harlequin</t>
+          <t>ARCHKEY SOLUTIONS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fenton, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
+          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ARCHKEY SOLUTIONS</t>
+          <t>Creative Global Consulting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fenton, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
+          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Creative Global Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Syncreon Consulting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Syncreon Consulting</t>
+          <t>ConcertAI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
+          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ConcertAI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
+          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Kafka API Gateway Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kafka API Gateway Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
+          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Software Engineer III - AWS, Python, Spark</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Python, Spark</t>
+          <t>Flask Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
+          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Flask Architect</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
+          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Deltasoft Solutions LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deltasoft Solutions LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>come and see</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>come and see</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
+          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>CooperCompanies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Henrietta, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,69 +1606,69 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
+          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CooperCompanies</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Henrietta, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Platform Engineer - Associate</t>
+          <t>Python/PySpark Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Python/PySpark Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
+          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
+          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
+          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
+          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
+          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,69 +2201,69 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
+          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,54 +2526,54 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CX Data Labs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CX Data Labs</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
+          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
         </is>
       </c>
     </row>
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
+          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Databricks Developer / Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>TruStartIT LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer / Data Engineer</t>
+          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TruStartIT LLC</t>
+          <t>Blue Sky Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Blue Sky Technology Solutions LLC</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Services</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Control Plane</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Aerospike</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Platform Engineer-AI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>Data Engineer - Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Scala Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4030,76 +4030,6 @@
         </is>
       </c>
       <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Data Engineer - Developer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Scala Architect</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
         </is>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,52 +853,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ARCHKEY SOLUTIONS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fenton, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mainframe Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Creative Global Consulting</t>
+          <t>Techmorgonite Software Solutions LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=82ad00171a071d4c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Syncreon Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Syncreon Consulting</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>CooperCompanies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Henrietta, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
+          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CooperCompanies</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Henrietta, NY, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Python/PySpark Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
+          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Python/PySpark Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
+          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, GCP, Dataflow, Kafka, MongoDB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffa64b4854cbdc5</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
+          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
+          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
+          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
+          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
+          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,59 +2246,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>IXIS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,77 +2516,77 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CX Data Labs</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>CX Data Labs</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
+          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer / Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TruStartIT LLC</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,29 +2726,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Blue Sky Technology Solutions LLC</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Senior Databricks Developer / Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>TruStartIT LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,77 +3006,77 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Kissimmee, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,24 +3461,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=48f4891dd9237660</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Services</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Control Plane</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Aerospike</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,67 +3681,67 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,59 +3751,59 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Integration Services Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
+          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer - Developer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
+          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Scala Architect</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,15 +4021,190 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer New</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Chantilly, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer-AI</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Thomson Reuters</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Plainview, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Data Engineer - Developer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Scala Architect</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
         </is>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (ServiceNow)</t>
+          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hotwire Communications</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (Tampa)</t>
+          <t>Senior Software Engineer (ServiceNow)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Hotwire Communications</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Data Engineer (Tampa)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
+          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
+          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HarperCollins Canada and Harlequin</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
+          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HarperCollins Canada and Harlequin</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mainframe Developer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Techmorgonite Software Solutions LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ad00171a071d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
+          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kafka API Gateway Engineer</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
+          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Kafka API Gateway Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deltasoft Solutions LLC</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>come and see</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>come and see</t>
+          <t>Deltasoft Solutions LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
+          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Platform Engineer - Associate</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Python/PySpark Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Python/PySpark Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Dataflow, Kafka, MongoDB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffa64b4854cbdc5</t>
+          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
+          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,182 +2096,182 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>IXIS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Test Analyst - ETL QA Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Panacea Direct Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
+          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IXIS</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,102 +2456,102 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
+          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,29 +2656,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CX Data Labs</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,172 +2806,172 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer / Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TruStartIT LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=b24d134a2f8c41f7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,102 +2981,102 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Integration Services Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,42 +3426,42 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kissimmee, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake, Tableau, Git, Python</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f4891dd9237660</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Senior Platform Engineer-AI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Integration Services Developer</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Services</t>
+          <t>Data Engineer - Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Control Plane</t>
+          <t>Scala Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Aerospike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3855,356 +3855,6 @@
         </is>
       </c>
       <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Kubernetes MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>AWS DevOps Data Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Railroad19</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Tesla</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>AMH</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Draper, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Chantilly, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer New</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Chantilly, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer-AI</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Thomson Reuters</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Texas Health and Human Services Commission</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Plainview, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Data Engineer - Developer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Scala Architect</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
         </is>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Engineer / Senior Platform Support Officer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.7</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ac562fdbccfcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=2833779a05dd416c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior Platform Support Officer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2833779a05dd416c</t>
+          <t>https://www.indeed.com/viewjob?jk=e53c61ac50aad63e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Senior Software Engineer (ServiceNow)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Hotwire Communications</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53c61ac50aad63e</t>
+          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
         </is>
       </c>
     </row>
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (ServiceNow)</t>
+          <t>Data Engineer (Tampa)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hotwire Communications</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer (Tampa)</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,24 +696,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -727,21 +727,21 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
+          <t>https://www.indeed.com/viewjob?jk=bc64b79d3e9d2292</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>HarperCollins Canada and Harlequin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
+          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HarperCollins Canada and Harlequin</t>
+          <t>ConcertAI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
+          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
+          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Syncreon Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - AWS, Python, Spark</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
+          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ConcertAI</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>come and see</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
+          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kafka API Gateway Engineer</t>
+          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deltasoft Solutions LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
+          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,137 +1196,137 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Python, Spark</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CooperCompanies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Henrietta, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
+          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Flask Architect</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
+          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Python/PySpark Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>come and see</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
+          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deltasoft Solutions LLC</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,49 +1476,49 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1532,46 +1532,46 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d18c7217c63ba8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CooperCompanies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Henrietta, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=eabc7140a8b5adbf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d3dc757eeb50099</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7c112e2eb3d06e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Python/PySpark Engineer</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,347 +1686,347 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
+          <t>https://www.indeed.com/viewjob?jk=ecf9acecdd49f852</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>IXIS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Test Analyst - ETL QA Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Panacea Direct Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Platform Engineer - Associate</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ac8b2469720423</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IXIS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,89 +2141,89 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
+          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2232,33 +2232,33 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Test Analyst - ETL QA Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Panacea Direct Inc</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2267,46 +2267,46 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
+          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,94 +2351,94 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Onsite - Sylmar, CA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Tutor Perini Corporation</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sylmar, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
+          <t>https://www.indeed.com/viewjob?jk=911f179152aa22b0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,137 +2596,137 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b24d134a2f8c41f7</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Integration Services Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,77 +3181,77 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,67 +3366,67 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Integration Services Developer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer - Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>SAP Security Administrator</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,262 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer New</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Chantilly, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer-AI</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Thomson Reuters</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud Services</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Roku</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Control Plane</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Aerospike</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Texas Health and Human Services Commission</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Plainview, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data Engineer - Developer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Scala Architect</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc64b79d3e9d2292</t>
+          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>HarperCollins Canada and Harlequin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HarperCollins Canada and Harlequin</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
+          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ConcertAI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
+          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ConcertAI</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
+          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
+          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer III - AWS, Python, Spark</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
+          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Python, Spark</t>
+          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deltasoft Solutions LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
+          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
+          <t>Oracle Fusion Technical Architect – Financials, Procurement &amp; HCM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deltasoft Solutions LLC</t>
+          <t>Desmata Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
+          <t>https://www.indeed.com/viewjob?jk=147edea2571f3c4a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>CooperCompanies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Henrietta, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
         </is>
       </c>
     </row>
@@ -1203,35 +1203,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CooperCompanies</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Henrietta, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Platform Engineer - Associate</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Test Analyst - ETL QA Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Panacea Direct Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d18c7217c63ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabc7140a8b5adbf</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3dc757eeb50099</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7c112e2eb3d06e</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Senior Data Engineer | Xbox Advertising</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecf9acecdd49f852</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Test Analyst - ETL QA Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Panacea Direct Inc</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ac8b2469720423</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,59 +2071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer - Onsite - Sylmar, CA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Tutor Perini Corporation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sylmar, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=911f179152aa22b0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf23ba78f8d81b1</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958ccdd251b4e97b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,102 +2351,102 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Onsite - Sylmar, CA</t>
+          <t>Enterprise Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tutor Perini Corporation</t>
+          <t>Ketjen</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sylmar, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, dbt</t>
+          <t>Kinesis, Azure, Databricks, Spark, Scala, Kafka, Snowflake, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911f179152aa22b0</t>
+          <t>https://www.indeed.com/viewjob?jk=8269b2aa63279467</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Integration Services Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Integration Services Developer</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Data Engineer - Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>SAP Security Administrator</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,365 +3251,15 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Tesla</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>AMH</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Draper, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Chantilly, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Bird Rides</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud Services</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Roku</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Control Plane</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Aerospike</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Texas Health and Human Services Commission</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Plainview, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Data Engineer - Developer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>SAP Security Administrator</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
         </is>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (ServiceNow)</t>
+          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hotwire Communications</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
+          <t>Senior Software Engineer (ServiceNow)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Hotwire Communications</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
+          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Sr. Site Reliability Engineer (Database focused)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HarperCollins Canada and Harlequin</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
+          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>HarperCollins Canada and Harlequin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ConcertAI</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
+          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ConcertAI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,137 +881,137 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
+          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
+          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Python, Spark</t>
+          <t>Full Stack Developer - Irving,TX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
+          <t>https://www.indeed.com/viewjob?jk=bd87b9fe8763cff2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deltasoft Solutions LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III - AWS, Python, Spark</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Security Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>come and see</t>
+          <t>SolarWinds</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
+          <t>AWS, Glue, IAM, RDS, Azure, SQL Server, PostgreSQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
+          <t>https://www.indeed.com/viewjob?jk=632d492ceb3b18b2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Oracle Fusion Technical Architect – Financials, Procurement &amp; HCM</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Desmata Inc</t>
+          <t>come and see</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147edea2571f3c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CooperCompanies</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Henrietta, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Deltasoft Solutions LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
+          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Platform Engineer - Associate</t>
+          <t>Oracle Fusion Technical Architect – Financials, Procurement &amp; HCM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Desmata Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=147edea2571f3c4a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Python/PySpark Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CooperCompanies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Henrietta, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
+          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Python/PySpark Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,157 +1501,157 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
+          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Test Analyst - ETL QA Engineer</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Panacea Direct Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Integration Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=f2388b8f06d12916</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Test Analyst - ETL QA Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>Panacea Direct Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>Software Engineer (ETL)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Radial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,129 +2001,129 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer - Onsite - Sylmar, CA</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tutor Perini Corporation</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sylmar, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911f179152aa22b0</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Data Engineer - Onsite - Sylmar, CA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tutor Perini Corporation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sylmar, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=911f179152aa22b0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,59 +2421,59 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Data, Analytics &amp; AI</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ketjen</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kinesis, Azure, Databricks, Spark, Scala, Kafka, Snowflake, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8269b2aa63279467</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>SQL Database Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GSK Solutions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Enterprise Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ketjen</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Kinesis, Azure, Databricks, Spark, Scala, Kafka, Snowflake, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=8269b2aa63279467</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Integration Services Developer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,112 +2866,112 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Services</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,49 +2981,49 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Control Plane</t>
+          <t>Integration Services Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Aerospike</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
+          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,15 +3033,15 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer - Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SAP Security Administrator</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,262 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Cloud Services</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Roku</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Control Plane</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Aerospike</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Great Gray Trust Company</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Plainview, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SAP Security Administrator</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Data Engineer - Developer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
+          <t>Senior Software Engineer (ServiceNow)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Hotwire Communications</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
+          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (ServiceNow)</t>
+          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hotwire Communications</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
+          <t>Oracle Fusion Technical Architect – Financials, Procurement &amp; HCM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deltasoft Solutions LLC</t>
+          <t>Desmata Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
+          <t>https://www.indeed.com/viewjob?jk=147edea2571f3c4a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Oracle Fusion Technical Architect – Financials, Procurement &amp; HCM</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Desmata Inc</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147edea2571f3c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>CooperCompanies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Henrietta, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
+          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CooperCompanies</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Henrietta, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Python/PySpark Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Python/PySpark Engineer</t>
+          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
+          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Integration Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=f2388b8f06d12916</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,77 +1501,77 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
+          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Platform Engineer - Associate</t>
+          <t>Senior Data Engineer | Xbox Advertising</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,94 +1581,94 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2388b8f06d12916</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>IXIS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Xbox Advertising</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Software Engineer (ETL)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IXIS</t>
+          <t>Radial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Test Analyst - ETL QA Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Panacea Direct Inc</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
+          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,129 +2001,129 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
+          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer - Onsite - Sylmar, CA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Tutor Perini Corporation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sylmar, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=911f179152aa22b0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Onsite - Sylmar, CA</t>
+          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tutor Perini Corporation</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sylmar, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, dbt</t>
+          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911f179152aa22b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>SQL Database Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>GSK Solutions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Enterprise Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Ketjen</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>Kinesis, Azure, Databricks, Spark, Scala, Kafka, Snowflake, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=8269b2aa63279467</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SQL Database Architect</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GSK Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Enterprise Data, Analytics &amp; AI</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ketjen</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,24 +2761,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kinesis, Azure, Databricks, Spark, Scala, Kafka, Snowflake, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8269b2aa63279467</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Integration Services Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,77 +2936,77 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Integration Services Developer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,19 +3226,19 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Application Architect- Amazon Connect SME</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=a3103510c5fb6dd9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=edff3222d9dfb35c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Services</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+          <t>https://www.indeed.com/viewjob?jk=83800f9abb3449f6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Control Plane</t>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Aerospike</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Data Engineer - Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
         </is>
       </c>
     </row>
@@ -3472,41 +3472,6 @@
       <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Data Engineer - Developer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (ServiceNow)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hotwire Communications</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
+          <t>https://www.indeed.com/viewjob?jk=52ebd75b55c0b878</t>
         </is>
       </c>
     </row>
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
+          <t>https://www.indeed.com/viewjob?jk=83cf0ba40f1b8d7f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (Tampa)</t>
+          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Engineer (Tampa)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,69 +696,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Database focused)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
+          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Sr. Site Reliability Engineer (Database focused)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HarperCollins Canada and Harlequin</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
+          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>HarperCollins Canada and Harlequin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ConcertAI</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
+          <t>https://www.indeed.com/viewjob?jk=8c87fe3f873334f0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
+          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
         </is>
       </c>
     </row>
@@ -1063,52 +1063,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>IAM Database Intelligence Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>come and see</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>come and see</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Platform Engineer - Associate</t>
+          <t>Integration Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=f2388b8f06d12916</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2388b8f06d12916</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior Data Engineer | Xbox Advertising</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Xbox Advertising</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
+          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>IXIS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IXIS</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Software Engineer (ETL)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Radial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,42 +1896,42 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Enterprise Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+          <t>https://www.indeed.com/viewjob?jk=1347a0b8d7916085</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, RDS, Spark, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,29 +2411,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SQL Database Architect</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GSK Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Data, Analytics &amp; AI</t>
+          <t>Automation Engineer (Mid level SDET)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ketjen</t>
+          <t>Medrio</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kinesis, Azure, Databricks, Spark, Scala, Kafka, Snowflake, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8269b2aa63279467</t>
+          <t>https://www.indeed.com/viewjob?jk=3b2f89f6db54cefa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SQL Database Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>GSK Solutions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ketjen</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>Kinesis, Azure, Databricks, Spark, Scala, Kafka, Snowflake, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+          <t>https://www.indeed.com/viewjob?jk=8269b2aa63279467</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Software Development Engineer 2 - Front-End</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Integration Services Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Artificial Intelligence &amp; Machine Learning Engineer, Associate</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,42 +2831,42 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, NoSQL, MLOps, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f0e9eb9da3b6fb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,94 +2876,94 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Integration Services Developer</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Application Architect- Amazon Connect SME</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=a3103510c5fb6dd9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Services</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+          <t>https://www.indeed.com/viewjob?jk=edff3222d9dfb35c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Control Plane</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Aerospike</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
+          <t>https://www.indeed.com/viewjob?jk=83800f9abb3449f6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Application Architect- Amazon Connect SME</t>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3103510c5fb6dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Invu Technology</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Jenkins, SonarQube</t>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff3222d9dfb35c</t>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Jenkins, SonarQube</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83800f9abb3449f6</t>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
+          <t>SAP Security Administrator</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3365,111 +3365,6 @@
         </is>
       </c>
       <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Texas Health and Human Services Commission</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Plainview, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Data Engineer - Developer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>SAP Security Administrator</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
         </is>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,47 +538,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53c61ac50aad63e</t>
+          <t>https://www.indeed.com/viewjob?jk=52ebd75b55c0b878</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ebd75b55c0b878</t>
+          <t>https://www.indeed.com/viewjob?jk=83cf0ba40f1b8d7f</t>
         </is>
       </c>
     </row>
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83cf0ba40f1b8d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
+          <t>Data Engineer (Tampa)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer (Tampa)</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
+          <t>https://www.indeed.com/viewjob?jk=4c8f77340c6b511f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b0c81573d731c6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Database focused)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
+          <t>https://www.indeed.com/viewjob?jk=02e266ae50f70115</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Sr. Site Reliability Engineer (Database focused)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HarperCollins Canada and Harlequin</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,112 +836,112 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
+          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>HarperCollins Canada and Harlequin</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c87fe3f873334f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fffefc8bffe04d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
+          <t>https://www.indeed.com/viewjob?jk=8c87fe3f873334f0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Irving,TX</t>
+          <t>Mainframe Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Techmorgonite Software Solutions LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,129 +951,129 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd87b9fe8763cff2</t>
+          <t>https://www.indeed.com/viewjob?jk=82ad00171a071d4c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
+          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Python, Spark</t>
+          <t>Full Stack Developer - Irving,TX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
+          <t>https://www.indeed.com/viewjob?jk=bd87b9fe8763cff2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Security Architect</t>
+          <t>Sr. PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SolarWinds</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, Azure, SQL Server, PostgreSQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632d492ceb3b18b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f58c5c3f56232c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IAM Database Intelligence Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,94 +1091,94 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Security Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>SolarWinds</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, IAM, RDS, Azure, SQL Server, PostgreSQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=632d492ceb3b18b2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>IAM Database Intelligence Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>come and see</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
+          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Oracle Fusion Technical Architect – Financials, Procurement &amp; HCM</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Desmata Inc</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147edea2571f3c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>come and see</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Oracle Fusion Technical Architect – Financials, Procurement &amp; HCM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CooperCompanies</t>
+          <t>Desmata Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Henrietta, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=147edea2571f3c4a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>S3, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,94 +1301,94 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
+          <t>https://www.indeed.com/viewjob?jk=ee79c7f5d1c28258</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Python/PySpark Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>CooperCompanies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Henrietta, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
+          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2388b8f06d12916</t>
+          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Python/PySpark Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
+          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Xbox Advertising</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Integration Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f2388b8f06d12916</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IXIS</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,77 +1581,77 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
+          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>World IT Center</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Hadoop, HDFS, Hive, HBase, Oozie, YARN, Impala, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=229e0051fc5c425c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer | Xbox Advertising</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>IXIS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>Senior Software Development Engineer of Test (SDET)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Westfield Insurance</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Westfield Center, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,42 +1886,42 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=f60d99cbbb8719ad</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer (ETL)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Radial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Security Engineer</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1347a0b8d7916085</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>ATG Entertainment</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer - Onsite - Sylmar, CA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tutor Perini Corporation</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sylmar, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911f179152aa22b0</t>
+          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,207 +2316,207 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=688b84fca2804c71</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Senior Bizops Engineer-1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b2ed1b7ac0e776d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=1347a0b8d7916085</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Automation Engineer (Mid level SDET)</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Medrio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b2f89f6db54cefa</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SQL Database Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GSK Solutions</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Cloud Storage, Spark, Scala, Kafka, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+          <t>https://www.indeed.com/viewjob?jk=7d74a8c2e0b3bc97</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Enterprise Data, Analytics &amp; AI</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ketjen</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kinesis, Azure, Databricks, Spark, Scala, Kafka, Snowflake, dbt, MLOps, CI/CD</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8269b2aa63279467</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2 - Front-End</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Integration Services Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Artificial Intelligence &amp; Machine Learning Engineer, Associate</t>
+          <t>Automation Engineer (Mid level SDET)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Medrio</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, NoSQL, MLOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f0e9eb9da3b6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=3b2f89f6db54cefa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>SQL Database Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>GSK Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Enterprise Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ketjen</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>Kinesis, Azure, Databricks, Spark, Scala, Kafka, Snowflake, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=8269b2aa63279467</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kissimmee, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+          <t>https://www.indeed.com/viewjob?jk=48f4891dd9237660</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Cloud Infrastructure Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+          <t>https://www.indeed.com/viewjob?jk=fae4f5e0a1b671f8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Development Engineer 2 - Front-End</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,102 +3051,102 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Control Plane</t>
+          <t>Integration Services Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Aerospike</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
+          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Application Architect- Amazon Connect SME</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3103510c5fb6dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Artificial Intelligence &amp; Machine Learning Engineer, Associate</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, NoSQL, MLOps, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff3222d9dfb35c</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f0e9eb9da3b6fb</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Jenkins, SonarQube</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83800f9abb3449f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Invu Technology</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SAP Security Administrator</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,367 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AWS DevOps Data Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Railroad19</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Application Architect- Amazon Connect SME</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3103510c5fb6dd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SAP Security Administrator</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer (Multi-Cloud &amp; AI Adoption)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Hyve Solutions</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61cdbfe08b450503</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edff3222d9dfb35c</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83800f9abb3449f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Great Gray Trust Company</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Invu Technology</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Plainview, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-18.xlsx
+++ b/results/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,82 +503,82 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior Platform Support Officer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>24.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2833779a05dd416c</t>
+          <t>https://www.indeed.com/viewjob?jk=008b82df0092f214</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>AI Engineer / Senior Platform Support Officer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ebd75b55c0b878</t>
+          <t>https://www.indeed.com/viewjob?jk=2833779a05dd416c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83cf0ba40f1b8d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=52ebd75b55c0b878</t>
         </is>
       </c>
     </row>
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
+          <t>https://www.indeed.com/viewjob?jk=83cf0ba40f1b8d7f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (Tampa)</t>
+          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Engineer (Tampa)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a3ce6fbd8495a1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,52 +731,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c8f77340c6b511f</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>SAP Data Migration Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b0c81573d731c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c6ffedc59232b1e6</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Database focused)</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
+          <t>https://www.indeed.com/viewjob?jk=a7230c31a417de52</t>
         </is>
       </c>
     </row>
@@ -888,25 +888,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Sr. Site Reliability Engineer (Database focused)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c87fe3f873334f0</t>
+          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mainframe Developer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Techmorgonite Software Solutions LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ad00171a071d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1885d139b3f38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Irving,TX</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd87b9fe8763cff2</t>
+          <t>https://www.indeed.com/viewjob?jk=c70566192b1dea40</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. PS Sales Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,77 +1046,77 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f58c5c3f56232c</t>
+          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr. PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f58c5c3f56232c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Security Architect</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SolarWinds</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, Azure, SQL Server, PostgreSQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632d492ceb3b18b2</t>
+          <t>https://www.indeed.com/viewjob?jk=b652d7f75551953a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IAM Database Intelligence Engineer</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,94 +1161,94 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>IAM Database Intelligence Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>come and see</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
+          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Oracle Fusion Technical Architect – Financials, Procurement &amp; HCM</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Desmata Inc</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147edea2571f3c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AI Infrastructure Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>come and see</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>S3, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee79c7f5d1c28258</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>CooperCompanies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Henrietta, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
+          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CooperCompanies</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Henrietta, NY, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2388b8f06d12916</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
         </is>
       </c>
     </row>
@@ -1588,70 +1588,70 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>World IT Center</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, HBase, Oozie, YARN, Impala, Spark, PySpark</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229e0051fc5c425c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Scientific Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6aeed34698c13e</t>
+          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Senior Data Engineer | Xbox Advertising</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Xbox Advertising</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>IXIS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
+          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer (ETL)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Radial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IXIS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer of Test (SDET)</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Westfield Insurance</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Westfield Center, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60d99cbbb8719ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Senior Software Engineer (Solutions)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>ATG Entertainment</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,42 +2026,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3ed0c65d630b07</t>
+          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ATG Entertainment</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
+          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Bizops Engineer-2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
+          <t>https://www.indeed.com/viewjob?jk=07739c1bad763116</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Product Engineer (Software/Java)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
+          <t>AWS, Scala, Kafka, ELT, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=13ad51a285cdcb71</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688b84fca2804c71</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Bizops Engineer-1</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b2ed1b7ac0e776d</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Security Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1347a0b8d7916085</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Gatik</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Spark, Scala, Kafka, Oracle, SQL Server, CI/CD</t>
+          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d74a8c2e0b3bc97</t>
+          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Claritas Rx</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, PostgreSQL, DynamoDB, ETL, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=5f338463dc36bfb7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518e23ecee84280c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LiveKit</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491dbd627fcfc1ec</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Automation Engineer (Mid level SDET)</t>
+          <t>Software Development Engineer 2 - Front-End</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Medrio</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b2f89f6db54cefa</t>
+          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SQL Database Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GSK Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Enterprise Data, Analytics &amp; AI</t>
+          <t>SQL Database Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ketjen</t>
+          <t>GSK Solutions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kinesis, Azure, Databricks, Spark, Scala, Kafka, Snowflake, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8269b2aa63279467</t>
+          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Integration Services Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kissimmee, FL, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake, Tableau, Git, Python</t>
+          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f4891dd9237660</t>
+          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GCP Cloud Infrastructure Architect</t>
+          <t>AWS SageMaker Data Scientist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,42 +2971,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae4f5e0a1b671f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8020b3571a5d8bac</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2 - Front-End</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Integration Services Developer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ESYSTEMS, INC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Artificial Intelligence &amp; Machine Learning Engineer, Associate</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, NoSQL, MLOps, Docker</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f0e9eb9da3b6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AWS DevOps Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Services</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4893fd8b3665a3</t>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Control Plane</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Aerospike</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Invu Technology</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AWS DevOps Data Engineer</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, IAM, RDS, Spark, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cadb7ee4495d97</t>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Application Architect- Amazon Connect SME</t>
+          <t>SAP Security Administrator</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,252 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3103510c5fb6dd9</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>SAP Security Administrator</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer (Multi-Cloud &amp; AI Adoption)</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Hyve Solutions</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Fremont, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61cdbfe08b450503</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edff3222d9dfb35c</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83800f9abb3449f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Great Gray Trust Company</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Invu Technology</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Texas Health and Human Services Commission</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Plainview, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
         </is>
       </c>
     </row>
